--- a/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4044,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5344,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -6102,7 +6102,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -6362,7 +6362,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6540,7 +6540,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6644,7 +6644,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LOS_OLIVOS</t>
+          <t>LOS OLIVOS</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>0001 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-11.92268</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.075</v>
-      </c>
-      <c r="I2" t="n">
-        <v>237</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-11.92268</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.075</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>0008 PEQUEÑO BENJAMIN</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-11.93757</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.07621</v>
-      </c>
-      <c r="I3" t="n">
-        <v>210</v>
-      </c>
-      <c r="J3" t="n">
-        <v>12</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-11.93757</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.07621</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>0013 PASTORCITOS DE FATIMA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-11.9641</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.0804</v>
-      </c>
-      <c r="I4" t="n">
-        <v>213</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-11.9641</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.0804</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>014 MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-11.97421</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.07526</v>
-      </c>
-      <c r="I5" t="n">
-        <v>204</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-11.97421</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.07526</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>018 OKINAWA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-11.9502</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.08179</v>
-      </c>
-      <c r="I6" t="n">
-        <v>362</v>
-      </c>
-      <c r="J6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-11.9502</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.08179</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>0318 CARMELITAS</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-11.98231</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.0667</v>
-      </c>
-      <c r="I7" t="n">
-        <v>203</v>
-      </c>
-      <c r="J7" t="n">
-        <v>11</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-11.98231</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.0667</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>0327 ALMIRANTE GRAU</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-11.9856</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.071</v>
-      </c>
-      <c r="I8" t="n">
-        <v>262</v>
-      </c>
-      <c r="J8" t="n">
-        <v>13</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-11.9856</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.071</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>0346 LAS PALMERAS</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-11.98773</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.07176</v>
-      </c>
-      <c r="I9" t="n">
-        <v>208</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-11.98773</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.07176</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>0348 SANTA LUISA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.95574</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.07155</v>
-      </c>
-      <c r="I10" t="n">
-        <v>237</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.95574</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.07155</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>0351 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.9965</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.0782</v>
-      </c>
-      <c r="I11" t="n">
-        <v>279</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.9965</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.0782</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>0375</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-11.97014</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.068534</v>
-      </c>
-      <c r="I12" t="n">
-        <v>255</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-11.97014</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.068534</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>0377 DIVINO NIÑO JESUS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-11.98246</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.07006</v>
-      </c>
-      <c r="I13" t="n">
-        <v>240</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-11.98246</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.07006</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>2004 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-11.97676</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.07872</v>
-      </c>
-      <c r="I14" t="n">
-        <v>537</v>
-      </c>
-      <c r="J14" t="n">
-        <v>24</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-11.97676</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.07872</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>2005 LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.01125</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.0792</v>
-      </c>
-      <c r="I15" t="n">
-        <v>538</v>
-      </c>
-      <c r="J15" t="n">
-        <v>24</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.01125</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.0792</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.00754</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.07722</v>
-      </c>
-      <c r="I16" t="n">
-        <v>753</v>
-      </c>
-      <c r="J16" t="n">
-        <v>32</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.00754</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.07722</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>2007 ROSA DE LAS AMERICAS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-11.98205</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.08295</v>
-      </c>
-      <c r="I17" t="n">
-        <v>959</v>
-      </c>
-      <c r="J17" t="n">
-        <v>40</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-11.98205</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.08295</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>2015 MANUEL GONZALEZ PRADA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-11.9954</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.06721</v>
-      </c>
-      <c r="I18" t="n">
-        <v>952</v>
-      </c>
-      <c r="J18" t="n">
-        <v>53</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-11.9954</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.06721</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>2016 CHAVIN DE HUANTAR</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.98506</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.07347</v>
-      </c>
-      <c r="I19" t="n">
-        <v>378</v>
-      </c>
-      <c r="J19" t="n">
-        <v>15</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.98506</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.07347</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-11.95047</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.08175</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1732</v>
-      </c>
-      <c r="J20" t="n">
-        <v>74</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-11.95047</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.08175</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>2025 INMACULADA CONCEPCION</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.945275</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.0746</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1438</v>
-      </c>
-      <c r="J21" t="n">
-        <v>67</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.945275</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.0746</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1438</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-11.9897</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.0778</v>
-      </c>
-      <c r="I22" t="n">
-        <v>400</v>
-      </c>
-      <c r="J22" t="n">
-        <v>17</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-11.9897</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.0778</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>2071 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.99395</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.07665</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1232</v>
-      </c>
-      <c r="J23" t="n">
-        <v>64</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.99395</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.07665</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1232</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>2078 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-11.9553</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-77.0712</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1554</v>
-      </c>
-      <c r="J24" t="n">
-        <v>78</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-11.9553</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-77.0712</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>2087 REPUBLICA ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-11.9684</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-77.06865000000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1072</v>
-      </c>
-      <c r="J25" t="n">
-        <v>54</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-11.9684</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-77.06865</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>2089 MICAELA BASTIDAS</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-11.987547</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-77.0667</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1154</v>
-      </c>
-      <c r="J26" t="n">
-        <v>56</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-11.987547</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-77.0667</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1154</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>2090 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-12.01</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-77.0735</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1082</v>
-      </c>
-      <c r="J27" t="n">
-        <v>57</v>
-      </c>
-      <c r="K27" t="n">
-        <v>1</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-12.01</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-77.0735</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>2091 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-11.98945</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-77.07302</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1482</v>
-      </c>
-      <c r="J28" t="n">
-        <v>68</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-11.98945</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-77.07302</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1482</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>2092 CRISTO MORADO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-11.99961</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-77.0754</v>
-      </c>
-      <c r="I29" t="n">
-        <v>482</v>
-      </c>
-      <c r="J29" t="n">
-        <v>26</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-11.99961</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-77.0754</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>2095 HERMAN BUSSE DE LA GUERRA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-11.9354</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-77.0746</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2300</v>
-      </c>
-      <c r="J30" t="n">
-        <v>98</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-11.9354</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-77.0746</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>2096 PERU JAPON</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-11.9802</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-77.06829999999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1004</v>
-      </c>
-      <c r="J31" t="n">
-        <v>45</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-11.9802</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-77.0683</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>3029</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-12.00308</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-77.06256999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>517</v>
-      </c>
-      <c r="J32" t="n">
-        <v>24</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-12.00308</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-77.06257</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>3078 HEROES DEL CENEPA</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-12.0037</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-77.0817</v>
-      </c>
-      <c r="I33" t="n">
-        <v>400</v>
-      </c>
-      <c r="J33" t="n">
-        <v>24</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-12.0037</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-77.0817</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>3080 PERU - CANADA</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-11.9558</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-77.07467</v>
-      </c>
-      <c r="I34" t="n">
-        <v>966</v>
-      </c>
-      <c r="J34" t="n">
-        <v>47</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-11.9558</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-77.07467</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>3087</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-11.9823</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-77.07145</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1494</v>
-      </c>
-      <c r="J35" t="n">
-        <v>63</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-11.9823</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-77.07145</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>3091</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-11.94144</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-77.076683</v>
-      </c>
-      <c r="I36" t="n">
-        <v>1332</v>
-      </c>
-      <c r="J36" t="n">
-        <v>61</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-11.94144</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-77.076683</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>3095 PERU KAWACHI</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-11.92235</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-77.07501999999999</v>
-      </c>
-      <c r="I37" t="n">
-        <v>992</v>
-      </c>
-      <c r="J37" t="n">
-        <v>53</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-11.92235</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-77.07502</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>JOSE ABELARDO QUIÑONEZ GONZALES</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-12.007857</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-77.063833</v>
-      </c>
-      <c r="I38" t="n">
-        <v>872</v>
-      </c>
-      <c r="J38" t="n">
-        <v>37</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-12.007857</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-77.063833</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>PNP PRECURSORES DE LA INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-11.95781</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-77.06849</v>
-      </c>
-      <c r="I39" t="n">
-        <v>740</v>
-      </c>
-      <c r="J39" t="n">
-        <v>43</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-11.95781</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-77.06849</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>PROYECTO INTEGRAL CHAVARRIA</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-12.0049</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-77.07592</v>
-      </c>
-      <c r="I40" t="n">
-        <v>761</v>
-      </c>
-      <c r="J40" t="n">
-        <v>42</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-12.0049</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-77.07592</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>NUEVO PERU</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-11.96896</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-77.0782</v>
-      </c>
-      <c r="I41" t="n">
-        <v>949</v>
-      </c>
-      <c r="J41" t="n">
-        <v>38</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-11.96896</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-77.0782</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>3047</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-11.94905</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-77.07250000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>317</v>
-      </c>
-      <c r="J42" t="n">
-        <v>13</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-11.94905</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-77.0725</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>PALMAS REALES</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-11.9933</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-77.07899999999999</v>
-      </c>
-      <c r="I43" t="n">
-        <v>638</v>
-      </c>
-      <c r="J43" t="n">
-        <v>46</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-11.9933</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-77.079</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>ALFREDO REBAZA ACOSTA</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-12.0032</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-77.0665</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1316</v>
-      </c>
-      <c r="J44" t="n">
-        <v>68</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-12.0032</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-77.0665</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>JORGE BASADRE GROHMANN</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-11.9827</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-77.0667</v>
-      </c>
-      <c r="I45" t="n">
-        <v>982</v>
-      </c>
-      <c r="J45" t="n">
-        <v>50</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-11.9827</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-77.0667</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-11.97452</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-77.06945</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1003</v>
-      </c>
-      <c r="J46" t="n">
-        <v>47</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-11.97452</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-77.06945</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>0022 SEMILLITAS DEL FUTURO</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-11.98813</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-77.0792</v>
-      </c>
-      <c r="I47" t="n">
-        <v>237</v>
-      </c>
-      <c r="J47" t="n">
-        <v>12</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-11.98813</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-77.0792</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>LOS LIBERTADORES</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-11.9807</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-77.07389999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>257</v>
-      </c>
-      <c r="J48" t="n">
-        <v>14</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-11.9807</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-77.0739</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>0025 CONFRATERNIDAD PERUANO - MEXICANO</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-11.9534</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-77.0834</v>
-      </c>
-      <c r="I49" t="n">
-        <v>243</v>
-      </c>
-      <c r="J49" t="n">
-        <v>11</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-11.9534</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-77.0834</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>0026 SAN ROQUE</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-11.9582</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-77.0766</v>
-      </c>
-      <c r="I50" t="n">
-        <v>306</v>
-      </c>
-      <c r="J50" t="n">
-        <v>13</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-11.9582</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-77.0766</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>BARBARA D'ACHILLE SCHOOL</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-11.96123</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-77.07379</v>
-      </c>
-      <c r="I51" t="n">
-        <v>231</v>
-      </c>
-      <c r="J51" t="n">
-        <v>18</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-11.96123</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-77.07379</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>BADEN POWELL</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-12.00838</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-77.07387</v>
-      </c>
-      <c r="I52" t="n">
-        <v>151</v>
-      </c>
-      <c r="J52" t="n">
-        <v>17</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-12.00838</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-77.07387</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>CORAZON DE JESUS PIONERO DE LA CIENCIA</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-11.9734</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-77.0843</v>
-      </c>
-      <c r="I53" t="n">
-        <v>448</v>
-      </c>
-      <c r="J53" t="n">
-        <v>39</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-11.9734</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-77.0843</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>DIVINO MAESTRO DE PRO</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-11.93312</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-77.07877000000001</v>
-      </c>
-      <c r="I54" t="n">
-        <v>485</v>
-      </c>
-      <c r="J54" t="n">
-        <v>58</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-11.93312</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-77.07877</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>PAMER CARLOS IZAGUIRRE</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-11.99119</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-77.08025000000001</v>
-      </c>
-      <c r="I55" t="n">
-        <v>615</v>
-      </c>
-      <c r="J55" t="n">
-        <v>24</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-11.99119</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-77.08025</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -3329,20 +3857,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G56" t="n">
-        <v>-11.97935</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-77.08188</v>
-      </c>
-      <c r="I56" t="n">
-        <v>355</v>
-      </c>
-      <c r="J56" t="n">
-        <v>27</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-11.97935</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-77.08188</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -3381,20 +3919,30 @@
           <t>ROBERT LETOURNEAU</t>
         </is>
       </c>
-      <c r="G57" t="n">
-        <v>-11.99529</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-77.06381</v>
-      </c>
-      <c r="I57" t="n">
-        <v>618</v>
-      </c>
-      <c r="J57" t="n">
-        <v>50</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-11.99529</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-77.06381</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3433,20 +3981,30 @@
           <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
-      <c r="G58" t="n">
-        <v>-11.98614</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-77.07040000000001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>389</v>
-      </c>
-      <c r="J58" t="n">
-        <v>27</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-11.98614</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-77.0704</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>389</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3485,20 +4043,30 @@
           <t>SAN MARCOS</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>-11.98264</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-77.07993</v>
-      </c>
-      <c r="I59" t="n">
-        <v>342</v>
-      </c>
-      <c r="J59" t="n">
-        <v>23</v>
-      </c>
-      <c r="K59" t="n">
-        <v>1</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-11.98264</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-77.07993</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -3537,20 +4105,30 @@
           <t>SANTA CECILIA DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>-11.97163</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-77.07286999999999</v>
-      </c>
-      <c r="I60" t="n">
-        <v>25</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3</v>
-      </c>
-      <c r="K60" t="n">
-        <v>1</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-11.97163</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-77.07287</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3589,20 +4167,30 @@
           <t>SANTA MARIA DE LA PROVIDENCIA</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>-11.99241</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-77.07804</v>
-      </c>
-      <c r="I61" t="n">
-        <v>684</v>
-      </c>
-      <c r="J61" t="n">
-        <v>28</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-11.99241</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-77.07804</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -3641,20 +4229,30 @@
           <t>JAHDAI</t>
         </is>
       </c>
-      <c r="G62" t="n">
-        <v>-11.991662</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-77.070904</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-11.991662</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-77.070904</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3693,20 +4291,30 @@
           <t>WILLIAM PRESCOTT</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>-11.99218</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-77.07908999999999</v>
-      </c>
-      <c r="I63" t="n">
-        <v>214</v>
-      </c>
-      <c r="J63" t="n">
-        <v>15</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-11.99218</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-77.07909</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3745,20 +4353,30 @@
           <t>BH SCHOOL</t>
         </is>
       </c>
-      <c r="G64" t="n">
-        <v>-11.97959</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-77.07473</v>
-      </c>
-      <c r="I64" t="n">
-        <v>664</v>
-      </c>
-      <c r="J64" t="n">
-        <v>38</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-11.97959</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-77.07473</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3797,20 +4415,30 @@
           <t>HANS CHRISTIAN</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>-11.94487</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-77.07658000000001</v>
-      </c>
-      <c r="I65" t="n">
-        <v>250</v>
-      </c>
-      <c r="J65" t="n">
-        <v>10</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-11.94487</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-77.07658</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3849,20 +4477,30 @@
           <t>CARITAS DE AMOR</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>-11.98579</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-77.07284</v>
-      </c>
-      <c r="I66" t="n">
-        <v>97</v>
-      </c>
-      <c r="J66" t="n">
-        <v>6</v>
-      </c>
-      <c r="K66" t="n">
-        <v>1</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-11.98579</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-77.07284</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,20 +4539,30 @@
           <t>LATINOAMERICANO</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>-11.9679</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-77.0827</v>
-      </c>
-      <c r="I67" t="n">
-        <v>257</v>
-      </c>
-      <c r="J67" t="n">
-        <v>12</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-11.9679</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-77.0827</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3953,20 +4601,30 @@
           <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>-11.965</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-77.06943</v>
-      </c>
-      <c r="I68" t="n">
-        <v>254</v>
-      </c>
-      <c r="J68" t="n">
-        <v>12</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-11.965</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-77.06943</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -4005,20 +4663,30 @@
           <t>SANTA MONICA COLLEGE</t>
         </is>
       </c>
-      <c r="G69" t="n">
-        <v>-11.94461</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-77.07437</v>
-      </c>
-      <c r="I69" t="n">
-        <v>371</v>
-      </c>
-      <c r="J69" t="n">
-        <v>21</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-11.94461</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-77.07437</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -4057,20 +4725,30 @@
           <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
-      <c r="G70" t="n">
-        <v>-11.98249</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-77.07059</v>
-      </c>
-      <c r="I70" t="n">
-        <v>405</v>
-      </c>
-      <c r="J70" t="n">
-        <v>16</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-11.98249</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-77.07059</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -4109,20 +4787,30 @@
           <t>MELITON CARVAJAL</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>-11.97868</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-77.07671000000001</v>
-      </c>
-      <c r="I71" t="n">
-        <v>66</v>
-      </c>
-      <c r="J71" t="n">
-        <v>6</v>
-      </c>
-      <c r="K71" t="n">
-        <v>2</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-11.97868</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-77.07671</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4161,20 +4849,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G72" t="n">
-        <v>-11.9956</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-77.0697</v>
-      </c>
-      <c r="I72" t="n">
-        <v>1971</v>
-      </c>
-      <c r="J72" t="n">
-        <v>151</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-11.9956</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-77.0697</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4213,20 +4911,30 @@
           <t>RAYITO DE LUNA</t>
         </is>
       </c>
-      <c r="G73" t="n">
-        <v>-11.93719</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-77.07714</v>
-      </c>
-      <c r="I73" t="n">
-        <v>282</v>
-      </c>
-      <c r="J73" t="n">
-        <v>13</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-11.93719</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-77.07714</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4265,20 +4973,30 @@
           <t>GALILEO GALILEI</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>-11.94887</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-77.07774999999999</v>
-      </c>
-      <c r="I74" t="n">
-        <v>200</v>
-      </c>
-      <c r="J74" t="n">
-        <v>24</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-11.94887</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-77.07775</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -4317,20 +5035,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G75" t="n">
-        <v>-12.006026</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-77.068613</v>
-      </c>
-      <c r="I75" t="n">
-        <v>228</v>
-      </c>
-      <c r="J75" t="n">
-        <v>14</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-12.006026</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-77.068613</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -4369,20 +5097,30 @@
           <t>STANFORD SUIZA PERUANA</t>
         </is>
       </c>
-      <c r="G76" t="n">
-        <v>-11.97634</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-77.07393</v>
-      </c>
-      <c r="I76" t="n">
-        <v>221</v>
-      </c>
-      <c r="J76" t="n">
-        <v>14</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-11.97634</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-77.07393</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4421,20 +5159,30 @@
           <t>SAN PABLO APOSTOL</t>
         </is>
       </c>
-      <c r="G77" t="n">
-        <v>-11.93901</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-77.07557</v>
-      </c>
-      <c r="I77" t="n">
-        <v>735</v>
-      </c>
-      <c r="J77" t="n">
-        <v>30</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-11.93901</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-77.07557</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>735</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4473,20 +5221,30 @@
           <t>SAN JUAN DE DIOS DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>-12.00696</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-77.07008</v>
-      </c>
-      <c r="I78" t="n">
-        <v>265</v>
-      </c>
-      <c r="J78" t="n">
-        <v>13</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-12.00696</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-77.07008</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4525,20 +5283,30 @@
           <t>SKHOLE PAIDEA DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G79" t="n">
-        <v>-11.99457</v>
-      </c>
-      <c r="H79" t="n">
-        <v>-77.07711999999999</v>
-      </c>
-      <c r="I79" t="n">
-        <v>49</v>
-      </c>
-      <c r="J79" t="n">
-        <v>5</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-11.99457</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-77.07712</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4577,20 +5345,30 @@
           <t>SAN VICENTE FERRER</t>
         </is>
       </c>
-      <c r="G80" t="n">
-        <v>-11.99345</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-77.07559999999999</v>
-      </c>
-      <c r="I80" t="n">
-        <v>2523</v>
-      </c>
-      <c r="J80" t="n">
-        <v>111</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-11.99345</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-77.0756</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2523</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4629,20 +5407,30 @@
           <t>SAN ANDRES</t>
         </is>
       </c>
-      <c r="G81" t="n">
-        <v>-11.92587</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-77.07339</v>
-      </c>
-      <c r="I81" t="n">
-        <v>340</v>
-      </c>
-      <c r="J81" t="n">
-        <v>21</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-11.92587</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-77.07339</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4681,20 +5469,30 @@
           <t>2028 PERUANO BRITANICO</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>-11.9693</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-77.0774</v>
-      </c>
-      <c r="I82" t="n">
-        <v>1387</v>
-      </c>
-      <c r="J82" t="n">
-        <v>63</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-11.9693</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-77.0774</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -4733,20 +5531,30 @@
           <t>INNOVA SCHOOLS - LOS OLIVOS VILLA SOL</t>
         </is>
       </c>
-      <c r="G83" t="n">
-        <v>-11.96243</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-77.07092</v>
-      </c>
-      <c r="I83" t="n">
-        <v>828</v>
-      </c>
-      <c r="J83" t="n">
-        <v>42</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-11.96243</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-77.07092</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4785,20 +5593,30 @@
           <t>ANDREAS VESALIUS</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>-11.991662</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-77.070904</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1</v>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-11.991662</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-77.070904</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4837,20 +5655,30 @@
           <t>INYARI</t>
         </is>
       </c>
-      <c r="G85" t="n">
-        <v>-12.00761</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-77.07084999999999</v>
-      </c>
-      <c r="I85" t="n">
-        <v>203</v>
-      </c>
-      <c r="J85" t="n">
-        <v>13</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-12.00761</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-77.07085</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4889,20 +5717,30 @@
           <t>PASITOS SEGUROS</t>
         </is>
       </c>
-      <c r="G86" t="n">
-        <v>-11.99136</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-77.0757</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="n">
-        <v>2</v>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-11.99136</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-77.0757</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4941,20 +5779,30 @@
           <t>NUESTRA SEÑORA DE MONSERRAT DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G87" t="n">
-        <v>-11.940858</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-77.07830300000001</v>
-      </c>
-      <c r="I87" t="n">
-        <v>478</v>
-      </c>
-      <c r="J87" t="n">
-        <v>32</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-11.940858</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-77.078303</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4993,20 +5841,30 @@
           <t>SACO OLIVEROS HELICOIDAL PALMERAS</t>
         </is>
       </c>
-      <c r="G88" t="n">
-        <v>-11.987933</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-77.077967</v>
-      </c>
-      <c r="I88" t="n">
-        <v>348</v>
-      </c>
-      <c r="J88" t="n">
-        <v>39</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-11.987933</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-77.077967</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5045,20 +5903,30 @@
           <t>SAN PIO X - LOS OLIVOS / SAN PIO X- LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G89" t="n">
-        <v>-11.99595</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-77.06654</v>
-      </c>
-      <c r="I89" t="n">
-        <v>947</v>
-      </c>
-      <c r="J89" t="n">
-        <v>64</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-11.99595</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-77.06654</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -5097,20 +5965,30 @@
           <t>JUAN XXIII DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G90" t="n">
-        <v>-11.94979</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-77.07984</v>
-      </c>
-      <c r="I90" t="n">
-        <v>270</v>
-      </c>
-      <c r="J90" t="n">
-        <v>19</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-11.94979</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-77.07984</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5149,20 +6027,30 @@
           <t>FRIEDERICH GAUSS</t>
         </is>
       </c>
-      <c r="G91" t="n">
-        <v>-12.00735</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-77.07723</v>
-      </c>
-      <c r="I91" t="n">
-        <v>287</v>
-      </c>
-      <c r="J91" t="n">
-        <v>14</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-12.00735</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-77.07723</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5201,20 +6089,30 @@
           <t>NUESTRA SEÑORA DE MONSERRAT DE MAYOLO</t>
         </is>
       </c>
-      <c r="G92" t="n">
-        <v>-11.99615</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-77.08086</v>
-      </c>
-      <c r="I92" t="n">
-        <v>238</v>
-      </c>
-      <c r="J92" t="n">
-        <v>15</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-11.99615</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-77.08086</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -5253,20 +6151,30 @@
           <t>CRISTO REY DE REYES</t>
         </is>
       </c>
-      <c r="G93" t="n">
-        <v>-11.9672</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-77.082033</v>
-      </c>
-      <c r="I93" t="n">
-        <v>214</v>
-      </c>
-      <c r="J93" t="n">
-        <v>17</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-11.9672</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-77.082033</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5305,20 +6213,30 @@
           <t>ISAAC NEWTON</t>
         </is>
       </c>
-      <c r="G94" t="n">
-        <v>-11.99562</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-77.07577999999999</v>
-      </c>
-      <c r="I94" t="n">
-        <v>99</v>
-      </c>
-      <c r="J94" t="n">
-        <v>13</v>
-      </c>
-      <c r="K94" t="n">
-        <v>1</v>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-11.99562</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-77.07578</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -5357,20 +6275,30 @@
           <t>NIÑOS DE MARIA</t>
         </is>
       </c>
-      <c r="G95" t="n">
-        <v>-11.9712</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-77.0732</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>2</v>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-11.9712</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-77.0732</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5409,20 +6337,30 @@
           <t>FRANCISCO PENZOTTI</t>
         </is>
       </c>
-      <c r="G96" t="n">
-        <v>-11.9669</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-77.0795</v>
-      </c>
-      <c r="I96" t="n">
-        <v>91</v>
-      </c>
-      <c r="J96" t="n">
-        <v>9</v>
-      </c>
-      <c r="K96" t="n">
-        <v>1</v>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-11.9669</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-77.0795</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5461,20 +6399,30 @@
           <t>ARQUITECTOS SCHOOL DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G97" t="n">
-        <v>-11.991662</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-77.070904</v>
-      </c>
-      <c r="I97" t="n">
-        <v>45</v>
-      </c>
-      <c r="J97" t="n">
-        <v>6</v>
-      </c>
-      <c r="K97" t="n">
-        <v>1</v>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-11.991662</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-77.070904</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5513,20 +6461,30 @@
           <t>HONORES DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G98" t="n">
-        <v>-11.98949</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-77.06573</v>
-      </c>
-      <c r="I98" t="n">
-        <v>274</v>
-      </c>
-      <c r="J98" t="n">
-        <v>23</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-11.98949</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>-77.06573</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5565,20 +6523,30 @@
           <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
-      <c r="G99" t="n">
-        <v>-11.98257</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-77.07093999999999</v>
-      </c>
-      <c r="I99" t="n">
-        <v>238</v>
-      </c>
-      <c r="J99" t="n">
-        <v>17</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0</v>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-11.98257</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>-77.07094</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5617,20 +6585,30 @@
           <t>CATOLICO SAN PIO X</t>
         </is>
       </c>
-      <c r="G100" t="n">
-        <v>-11.99521</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-77.06437</v>
-      </c>
-      <c r="I100" t="n">
-        <v>384</v>
-      </c>
-      <c r="J100" t="n">
-        <v>42</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-11.99521</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-77.06437</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5669,20 +6647,30 @@
           <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
-      <c r="G101" t="n">
-        <v>-11.9672</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-77.08199999999999</v>
-      </c>
-      <c r="I101" t="n">
-        <v>293</v>
-      </c>
-      <c r="J101" t="n">
-        <v>31</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-11.9672</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>-77.082</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -5721,20 +6709,30 @@
           <t>LUMEN DEI</t>
         </is>
       </c>
-      <c r="G102" t="n">
-        <v>-11.99255</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-77.06475</v>
-      </c>
-      <c r="I102" t="n">
-        <v>43</v>
-      </c>
-      <c r="J102" t="n">
-        <v>2</v>
-      </c>
-      <c r="K102" t="n">
-        <v>1</v>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-11.99255</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-77.06475</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5773,20 +6771,30 @@
           <t>CRUZ SACO</t>
         </is>
       </c>
-      <c r="G103" t="n">
-        <v>-11.98971</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-77.06518</v>
-      </c>
-      <c r="I103" t="n">
-        <v>213</v>
-      </c>
-      <c r="J103" t="n">
-        <v>16</v>
-      </c>
-      <c r="K103" t="n">
-        <v>1</v>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-11.98971</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-77.06518</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5825,20 +6833,30 @@
           <t>SAN LUIS GONZAGA SCHOOL</t>
         </is>
       </c>
-      <c r="G104" t="n">
-        <v>-11.95634</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-77.06569</v>
-      </c>
-      <c r="I104" t="n">
-        <v>352</v>
-      </c>
-      <c r="J104" t="n">
-        <v>22</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-11.95634</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-77.06569</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5877,20 +6895,30 @@
           <t>ILLARI</t>
         </is>
       </c>
-      <c r="G105" t="n">
-        <v>-11.99251</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-77.07073</v>
-      </c>
-      <c r="I105" t="n">
-        <v>29</v>
-      </c>
-      <c r="J105" t="n">
-        <v>3</v>
-      </c>
-      <c r="K105" t="n">
-        <v>1</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-11.99251</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-77.07073</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -5929,20 +6957,30 @@
           <t>MUNDO FELIZ KINDERGARTEN &amp; PRIMARY SCHOOL</t>
         </is>
       </c>
-      <c r="G106" t="n">
-        <v>-11.93763</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-77.07844</v>
-      </c>
-      <c r="I106" t="n">
-        <v>127</v>
-      </c>
-      <c r="J106" t="n">
-        <v>10</v>
-      </c>
-      <c r="K106" t="n">
-        <v>1</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-11.93763</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-77.07844</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -5981,20 +7019,30 @@
           <t>GOTITAS DE AMOR</t>
         </is>
       </c>
-      <c r="G107" t="n">
-        <v>-12.00611</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-77.08073</v>
-      </c>
-      <c r="I107" t="n">
-        <v>4</v>
-      </c>
-      <c r="J107" t="n">
-        <v>2</v>
-      </c>
-      <c r="K107" t="n">
-        <v>1</v>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-12.00611</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-77.08073</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -6033,20 +7081,30 @@
           <t>TRILCE LOS OLIVOS DE PROLIMA</t>
         </is>
       </c>
-      <c r="G108" t="n">
-        <v>-11.92709</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-77.07332</v>
-      </c>
-      <c r="I108" t="n">
-        <v>1926</v>
-      </c>
-      <c r="J108" t="n">
-        <v>76</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-11.92709</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-77.07332</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1926</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -6085,20 +7143,30 @@
           <t>SACO OLIVEROS</t>
         </is>
       </c>
-      <c r="G109" t="n">
-        <v>-11.96696</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-77.07281</v>
-      </c>
-      <c r="I109" t="n">
-        <v>1519</v>
-      </c>
-      <c r="J109" t="n">
-        <v>54</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-11.96696</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-77.07281</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -6137,20 +7205,30 @@
           <t>TECHNOLOGY SCHOOLS LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G110" t="n">
-        <v>-11.935869</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-77.079397</v>
-      </c>
-      <c r="I110" t="n">
-        <v>315</v>
-      </c>
-      <c r="J110" t="n">
-        <v>22</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-11.935869</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-77.079397</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -6189,20 +7267,30 @@
           <t>CONSUELO VALLEJOS</t>
         </is>
       </c>
-      <c r="G111" t="n">
-        <v>-11.95436</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-77.07228000000001</v>
-      </c>
-      <c r="I111" t="n">
-        <v>282</v>
-      </c>
-      <c r="J111" t="n">
-        <v>20</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0</v>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-11.95436</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-77.07228</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -6241,20 +7329,30 @@
           <t>PEREGRINOS DEL SEÑOR</t>
         </is>
       </c>
-      <c r="G112" t="n">
-        <v>-11.97344</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-77.07317999999999</v>
-      </c>
-      <c r="I112" t="n">
-        <v>209</v>
-      </c>
-      <c r="J112" t="n">
-        <v>13</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0</v>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-11.97344</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-77.07318</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -6293,20 +7391,30 @@
           <t>VISIONARIOS COLEGIO</t>
         </is>
       </c>
-      <c r="G113" t="n">
-        <v>-11.96155</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-77.07104</v>
-      </c>
-      <c r="I113" t="n">
-        <v>458</v>
-      </c>
-      <c r="J113" t="n">
-        <v>65</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0</v>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-11.96155</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-77.07104</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -6345,20 +7453,30 @@
           <t>SAN VICENTE FERRER</t>
         </is>
       </c>
-      <c r="G114" t="n">
-        <v>-11.92672</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-77.07374</v>
-      </c>
-      <c r="I114" t="n">
-        <v>310</v>
-      </c>
-      <c r="J114" t="n">
-        <v>17</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-11.92672</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-77.07374</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -6397,20 +7515,30 @@
           <t>JULIO REY PASTOR</t>
         </is>
       </c>
-      <c r="G115" t="n">
-        <v>-11.9495</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-77.0847</v>
-      </c>
-      <c r="I115" t="n">
-        <v>86</v>
-      </c>
-      <c r="J115" t="n">
-        <v>9</v>
-      </c>
-      <c r="K115" t="n">
-        <v>1</v>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-11.9495</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-77.0847</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
@@ -6449,20 +7577,30 @@
           <t>CORAZON DE JESUS PIONERO DE LA CIENCIA - SEDE SANTA LUISA</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>-11.95345</v>
-      </c>
-      <c r="H116" t="n">
-        <v>-77.0719</v>
-      </c>
-      <c r="I116" t="n">
-        <v>325</v>
-      </c>
-      <c r="J116" t="n">
-        <v>20</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-11.95345</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-77.0719</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
@@ -6501,20 +7639,30 @@
           <t>SAN IGNACIO DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G117" t="n">
-        <v>-11.94956</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-77.07375999999999</v>
-      </c>
-      <c r="I117" t="n">
-        <v>265</v>
-      </c>
-      <c r="J117" t="n">
-        <v>13</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-11.94956</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-77.07376</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
@@ -6553,20 +7701,30 @@
           <t>PITAGORAS</t>
         </is>
       </c>
-      <c r="G118" t="n">
-        <v>-11.99284</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-77.06999</v>
-      </c>
-      <c r="I118" t="n">
-        <v>546</v>
-      </c>
-      <c r="J118" t="n">
-        <v>30</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-11.99284</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-77.06999</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -6605,20 +7763,30 @@
           <t>INNOVA SCHOOLS - LOS OLIVOS SANTA ANA</t>
         </is>
       </c>
-      <c r="G119" t="n">
-        <v>-11.951</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-77.07792000000001</v>
-      </c>
-      <c r="I119" t="n">
-        <v>1403</v>
-      </c>
-      <c r="J119" t="n">
-        <v>60</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-11.951</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-77.07792</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
@@ -6657,20 +7825,30 @@
           <t>NUESTRA SEÑORA DE MONSERRAT DE SAN MARTIN</t>
         </is>
       </c>
-      <c r="G120" t="n">
-        <v>-11.990949</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-77.08069</v>
-      </c>
-      <c r="I120" t="n">
-        <v>336</v>
-      </c>
-      <c r="J120" t="n">
-        <v>19</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-11.990949</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-77.08069</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -6709,20 +7887,30 @@
           <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>-11.93341</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-77.07339</v>
-      </c>
-      <c r="I121" t="n">
-        <v>217</v>
-      </c>
-      <c r="J121" t="n">
-        <v>11</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0</v>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-11.93341</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-77.07339</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -6761,20 +7949,30 @@
           <t>LA RECOLETA DE LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>-11.957012</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-77.07495400000001</v>
-      </c>
-      <c r="I122" t="n">
-        <v>396</v>
-      </c>
-      <c r="J122" t="n">
-        <v>15</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0</v>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-11.957012</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-77.074954</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -6813,20 +8011,30 @@
           <t>MANUEL DUATO</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>-11.99665</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-77.06843000000001</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0</v>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-11.99665</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-77.06843</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>310696</t>
+          <t>312172</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0001 NIÑO JESUS DE PRAGA</t>
+          <t>JAHDAI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.92268</t>
+          <t>-11.991662</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.075</t>
+          <t>-77.070904</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>310700</t>
+          <t>528285</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0008 PEQUEÑO BENJAMIN</t>
+          <t>ANDREAS VESALIUS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.93757</t>
+          <t>-11.991662</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.07621</t>
+          <t>-77.070904</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>310719</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0013 PASTORCITOS DE FATIMA</t>
+          <t>PASITOS SEGUROS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.9641</t>
+          <t>-11.99136</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.0804</t>
+          <t>-77.0757</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>310724</t>
+          <t>695694</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>014 MARIA AUXILIADORA</t>
+          <t>NIÑOS DE MARIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.97421</t>
+          <t>-11.9712</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.07526</t>
+          <t>-77.0732</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>310757</t>
+          <t>313096</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>018 OKINAWA</t>
+          <t>MANUEL DUATO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.9502</t>
+          <t>-11.99665</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.08179</t>
+          <t>-77.06843</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>310762</t>
+          <t>312493</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0318 CARMELITAS</t>
+          <t>HANS CHRISTIAN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.98231</t>
+          <t>-11.94487</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>-77.07658</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>310776</t>
+          <t>698131</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0327 ALMIRANTE GRAU</t>
+          <t>MUNDO FELIZ KINDERGARTEN &amp; PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.9856</t>
+          <t>-11.93763</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.071</t>
+          <t>-77.07844</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>127</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,27 +935,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>310804</t>
+          <t>310696</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0346 LAS PALMERAS</t>
+          <t>0001 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.98773</t>
+          <t>-11.92268</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.07176</t>
+          <t>-77.075</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>310818</t>
+          <t>310762</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0348 SANTA LUISA</t>
+          <t>0318 CARMELITAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.95574</t>
+          <t>-11.98231</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.07155</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>310823</t>
+          <t>310804</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0351 SAN MARTIN DE PORRES</t>
+          <t>0346 LAS PALMERAS</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.9965</t>
+          <t>-11.98773</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.0782</t>
+          <t>-77.07176</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>208</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,27 +1121,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>310837</t>
+          <t>310818</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0348 SANTA LUISA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.97014</t>
+          <t>-11.95574</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.068534</t>
+          <t>-77.07155</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>310842</t>
+          <t>310837</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0377 DIVINO NIÑO JESUS</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.98246</t>
+          <t>-11.97014</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.07006</t>
+          <t>-77.068534</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>255</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>310861</t>
+          <t>311295</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2004 SEÑOR DE LOS MILAGROS</t>
+          <t>0025 CONFRATERNIDAD PERUANO - MEXICANO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.97676</t>
+          <t>-11.9534</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.07872</t>
+          <t>-77.0834</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>243</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>310875</t>
+          <t>857785</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2005 LOS OLIVOS</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-12.01125</t>
+          <t>-11.93341</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.0792</t>
+          <t>-77.07339</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>217</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>310880</t>
+          <t>313478</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>SAN VICENTE FERRER</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-12.00754</t>
+          <t>-11.99345</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.07722</t>
+          <t>-77.0756</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>310899</t>
+          <t>310700</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2007 ROSA DE LAS AMERICAS</t>
+          <t>0008 PEQUEÑO BENJAMIN</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.98205</t>
+          <t>-11.93757</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.08295</t>
+          <t>-77.07621</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>210</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>310903</t>
+          <t>310842</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2015 MANUEL GONZALEZ PRADA</t>
+          <t>0377 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.9954</t>
+          <t>-11.98246</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.06721</t>
+          <t>-77.07006</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>240</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>310917</t>
+          <t>311257</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2016 CHAVIN DE HUANTAR</t>
+          <t>0022 SEMILLITAS DEL FUTURO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.98506</t>
+          <t>-11.98813</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.07347</t>
+          <t>-77.0792</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>237</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>310936</t>
+          <t>312596</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>LATINOAMERICANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.95047</t>
+          <t>-11.9679</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.08175</t>
+          <t>-77.0827</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>310941</t>
+          <t>312676</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025 INMACULADA CONCEPCION</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.945275</t>
+          <t>-11.965</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.0746</t>
+          <t>-77.06943</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>310955</t>
+          <t>310776</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
+          <t>0327 ALMIRANTE GRAU</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.9897</t>
+          <t>-11.9856</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.0778</t>
+          <t>-77.071</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>262</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>310960</t>
+          <t>310823</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2071 CESAR VALLEJO</t>
+          <t>0351 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.99395</t>
+          <t>-11.9965</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.07665</t>
+          <t>-77.0782</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>310979</t>
+          <t>311196</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2078 NUESTRA SEÑORA DE LOURDES</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.9553</t>
+          <t>-11.94905</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.0712</t>
+          <t>-77.0725</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>317</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>310984</t>
+          <t>311304</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2087 REPUBLICA ORIENTAL DEL URUGUAY</t>
+          <t>0026 SAN ROQUE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.9684</t>
+          <t>-11.9582</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.06865</t>
+          <t>-77.0766</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>306</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>310998</t>
+          <t>313058</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2089 MICAELA BASTIDAS</t>
+          <t>RAYITO DE LUNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.987547</t>
+          <t>-11.93719</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>-77.07714</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,42 +2051,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>311002</t>
+          <t>313384</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2090 VIRGEN DE LA PUERTA</t>
+          <t>SAN JUAN DE DIOS DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.01</t>
+          <t>-12.00696</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.0735</t>
+          <t>-77.07008</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>311016</t>
+          <t>545497</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2091 MARISCAL ANDRES AVELINO CACERES</t>
+          <t>INYARI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-11.98945</t>
+          <t>-12.00761</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.07302</t>
+          <t>-77.07085</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>203</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>311021</t>
+          <t>695062</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2092 CRISTO MORADO</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.99961</t>
+          <t>-11.99562</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.0754</t>
+          <t>-77.07578</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>311035</t>
+          <t>755536</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2095 HERMAN BUSSE DE LA GUERRA</t>
+          <t>PEREGRINOS DEL SEÑOR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.9354</t>
+          <t>-11.97344</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.0746</t>
+          <t>-77.07318</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>209</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>311040</t>
+          <t>812792</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2096 PERU JAPON</t>
+          <t>SAN IGNACIO DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.9802</t>
+          <t>-11.94956</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.0683</t>
+          <t>-77.07376</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>311059</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-12.00308</t>
+          <t>-11.9807</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.06257</t>
+          <t>-77.0739</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>311078</t>
+          <t>313124</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>3078 HEROES DEL CENEPA</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.0037</t>
+          <t>-12.006026</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.0817</t>
+          <t>-77.068613</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>228</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>311083</t>
+          <t>313143</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3080 PERU - CANADA</t>
+          <t>STANFORD SUIZA PERUANA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.9558</t>
+          <t>-11.97634</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.07467</t>
+          <t>-77.07393</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>221</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>311101</t>
+          <t>694374</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>FRIEDERICH GAUSS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-11.9823</t>
+          <t>-12.00735</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.07145</t>
+          <t>-77.07723</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>287</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>311115</t>
+          <t>310757</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>018 OKINAWA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.94144</t>
+          <t>-11.9502</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.076683</t>
+          <t>-77.08179</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>362</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>311120</t>
+          <t>310917</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3095 PERU KAWACHI</t>
+          <t>2016 CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.92235</t>
+          <t>-11.98506</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.07502</t>
+          <t>-77.07347</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>378</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>311144</t>
+          <t>312271</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>JOSE ABELARDO QUIÑONEZ GONZALES</t>
+          <t>WILLIAM PRESCOTT</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-12.007857</t>
+          <t>-11.99218</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.063833</t>
+          <t>-77.07909</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>311158</t>
+          <t>694393</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PNP PRECURSORES DE LA INDEPENDENCIA NACIONAL</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE MAYOLO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.95781</t>
+          <t>-11.99615</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.06849</t>
+          <t>-77.08086</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>311163</t>
+          <t>865785</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PROYECTO INTEGRAL CHAVARRIA</t>
+          <t>LA RECOLETA DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-12.0049</t>
+          <t>-11.957012</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.07592</t>
+          <t>-77.074954</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>396</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>311182</t>
+          <t>312997</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NUEVO PERU</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.96896</t>
+          <t>-11.9956</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.0782</t>
+          <t>-77.0697</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>151</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>311196</t>
+          <t>312935</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.94905</t>
+          <t>-11.98249</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.0725</t>
+          <t>-77.07059</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>405</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3043,42 +3043,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>311200</t>
+          <t>697075</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PALMAS REALES</t>
+          <t>CRUZ SACO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.9933</t>
+          <t>-11.98971</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.079</t>
+          <t>-77.06518</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>311219</t>
+          <t>310955</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ALFREDO REBAZA ACOSTA</t>
+          <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-12.0032</t>
+          <t>-11.9897</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.0665</t>
+          <t>-77.0778</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>311224</t>
+          <t>311356</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHMANN</t>
+          <t>BADEN POWELL</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-11.9827</t>
+          <t>-12.00838</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>-77.07387</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>151</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>311238</t>
+          <t>694500</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
+          <t>CRISTO REY DE REYES</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.97452</t>
+          <t>-11.9672</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.06945</t>
+          <t>-77.082033</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>214</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>311257</t>
+          <t>696330</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0022 SEMILLITAS DEL FUTURO</t>
+          <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.98813</t>
+          <t>-11.98257</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.0792</t>
+          <t>-77.07094</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>238</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>311281</t>
+          <t>780017</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LOS LIBERTADORES</t>
+          <t>SAN VICENTE FERRER</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.9807</t>
+          <t>-11.92672</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.0739</t>
+          <t>-77.07374</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>311295</t>
+          <t>311342</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0025 CONFRATERNIDAD PERUANO - MEXICANO</t>
+          <t>BARBARA D'ACHILLE SCHOOL</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.9534</t>
+          <t>-11.96123</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.0834</t>
+          <t>-77.07379</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>311304</t>
+          <t>649758</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0026 SAN ROQUE</t>
+          <t>JUAN XXIII DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.9582</t>
+          <t>-11.94979</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.0766</t>
+          <t>-77.07984</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>311342</t>
+          <t>837882</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BARBARA D'ACHILLE SCHOOL</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.96123</t>
+          <t>-11.990949</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.07379</t>
+          <t>-77.08069</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>336</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>311356</t>
+          <t>696882</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BADEN POWELL</t>
+          <t>LUMEN DEI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-12.00838</t>
+          <t>-11.99255</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.07387</t>
+          <t>-77.06475</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,42 +3663,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>311436</t>
+          <t>698697</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA</t>
+          <t>GOTITAS DE AMOR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-11.9734</t>
+          <t>-12.00611</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.0843</t>
+          <t>-77.08073</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3725,32 +3725,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>311484</t>
+          <t>751604</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO DE PRO</t>
+          <t>CONSUELO VALLEJOS</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.93312</t>
+          <t>-11.95436</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.07877</t>
+          <t>-77.07228</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>282</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>311610</t>
+          <t>783520</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PAMER CARLOS IZAGUIRRE</t>
+          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA - SEDE SANTA LUISA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.99119</t>
+          <t>-11.95345</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.08025</t>
+          <t>-77.0719</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3849,32 +3849,32 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>311894</t>
+          <t>312841</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>SANTA MONICA COLLEGE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-11.97935</t>
+          <t>-11.94461</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-77.08188</t>
+          <t>-77.07437</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>371</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>311931</t>
+          <t>313529</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>ROBERT LETOURNEAU</t>
+          <t>SAN ANDRES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.99529</t>
+          <t>-11.92587</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.06381</t>
+          <t>-77.07339</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>340</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>312025</t>
+          <t>697122</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
+          <t>SAN LUIS GONZAGA SCHOOL</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.98614</t>
+          <t>-11.95634</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.0704</t>
+          <t>-77.06569</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>352</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4035,42 +4035,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>312054</t>
+          <t>745547</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>TECHNOLOGY SCHOOLS LOS OLIVOS</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.98264</t>
+          <t>-11.935869</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.07993</t>
+          <t>-77.079397</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>315</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4097,32 +4097,32 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>312110</t>
+          <t>312054</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SANTA CECILIA DE LOS OLIVOS</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.97163</t>
+          <t>-11.98264</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.07287</t>
+          <t>-77.07993</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>342</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>312167</t>
+          <t>696245</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE LA PROVIDENCIA</t>
+          <t>HONORES DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.99241</t>
+          <t>-11.98949</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.07804</t>
+          <t>-77.06573</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4221,37 +4221,37 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>312172</t>
+          <t>310861</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>JAHDAI</t>
+          <t>2004 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.991662</t>
+          <t>-11.97676</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.070904</t>
+          <t>-77.07872</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>537</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>312271</t>
+          <t>310875</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>WILLIAM PRESCOTT</t>
+          <t>2005 LOS OLIVOS</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-11.99218</t>
+          <t>-12.01125</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.07909</t>
+          <t>-77.0792</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>538</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>312290</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BH SCHOOL</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-11.97959</t>
+          <t>-12.00308</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.07473</t>
+          <t>-77.06257</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>517</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4407,32 +4407,32 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>312493</t>
+          <t>311078</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>HANS CHRISTIAN</t>
+          <t>3078 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-11.94487</t>
+          <t>-12.0037</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.07658</t>
+          <t>-77.0817</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>400</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>312520</t>
+          <t>311610</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CARITAS DE AMOR</t>
+          <t>PAMER CARLOS IZAGUIRRE</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.98579</t>
+          <t>-11.99119</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.07284</t>
+          <t>-77.08025</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>615</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>312596</t>
+          <t>313063</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LATINOAMERICANO</t>
+          <t>GALILEO GALILEI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.9679</t>
+          <t>-11.94887</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.0827</t>
+          <t>-77.07775</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>312676</t>
+          <t>311021</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>2092 CRISTO MORADO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.965</t>
+          <t>-11.99961</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.06943</t>
+          <t>-77.0754</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>482</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4655,32 +4655,32 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>312841</t>
+          <t>311894</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SANTA MONICA COLLEGE</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>-11.94461</t>
+          <t>-11.97935</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-77.07437</t>
+          <t>-77.08188</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>355</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>312935</t>
+          <t>312025</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE QUIVES</t>
+          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.98249</t>
+          <t>-11.98614</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.07059</t>
+          <t>-77.0704</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>389</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4779,37 +4779,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>312940</t>
+          <t>312167</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MELITON CARVAJAL</t>
+          <t>SANTA MARIA DE LA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.97868</t>
+          <t>-11.99241</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.07671</t>
+          <t>-77.07804</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>684</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>312997</t>
+          <t>312110</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>SANTA CECILIA DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.9956</t>
+          <t>-11.97163</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.0697</t>
+          <t>-77.07287</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -4903,37 +4903,37 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>313058</t>
+          <t>697481</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>RAYITO DE LUNA</t>
+          <t>ILLARI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.93719</t>
+          <t>-11.99251</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.07714</t>
+          <t>-77.07073</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>313063</t>
+          <t>313303</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>GALILEO GALILEI</t>
+          <t>SAN PABLO APOSTOL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.94887</t>
+          <t>-11.93901</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.07775</t>
+          <t>-77.07557</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>735</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>313124</t>
+          <t>832422</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-12.006026</t>
+          <t>-11.99284</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.068613</t>
+          <t>-77.06999</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>313143</t>
+          <t>696655</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>STANFORD SUIZA PERUANA</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.97634</t>
+          <t>-11.9672</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.07393</t>
+          <t>-77.082</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>293</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>313303</t>
+          <t>310880</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>SAN PABLO APOSTOL</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-11.93901</t>
+          <t>-12.00754</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.07557</t>
+          <t>-77.07722</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>753</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>313384</t>
+          <t>578497</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS DE LOS OLIVOS</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-12.00696</t>
+          <t>-11.940858</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.07008</t>
+          <t>-77.078303</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>478</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,37 +5275,37 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>313459</t>
+          <t>311144</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SKHOLE PAIDEA DE LOS OLIVOS</t>
+          <t>JOSE ABELARDO QUIÑONEZ GONZALES</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-11.99457</t>
+          <t>-12.007857</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.07712</t>
+          <t>-77.063833</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>872</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>313478</t>
+          <t>311182</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SAN VICENTE FERRER</t>
+          <t>NUEVO PERU</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.99345</t>
+          <t>-11.96896</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.0756</t>
+          <t>-77.0782</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>949</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>313529</t>
+          <t>312290</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SAN ANDRES</t>
+          <t>BH SCHOOL</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.92587</t>
+          <t>-11.97959</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.07339</t>
+          <t>-77.07473</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>664</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>333099</t>
+          <t>311436</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2028 PERUANO BRITANICO</t>
+          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.9693</t>
+          <t>-11.9734</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.0774</t>
+          <t>-77.0843</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>448</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>357537</t>
+          <t>644483</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - LOS OLIVOS VILLA SOL</t>
+          <t>SACO OLIVEROS HELICOIDAL PALMERAS</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.96243</t>
+          <t>-11.987933</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.07092</t>
+          <t>-77.077967</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5585,37 +5585,37 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>528285</t>
+          <t>310899</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ANDREAS VESALIUS</t>
+          <t>2007 ROSA DE LAS AMERICAS</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.991662</t>
+          <t>-11.98205</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.070904</t>
+          <t>-77.08295</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>959</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5647,32 +5647,32 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>545497</t>
+          <t>311163</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>INYARI</t>
+          <t>PROYECTO INTEGRAL CHAVARRIA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-12.00761</t>
+          <t>-12.0049</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-77.07085</t>
+          <t>-77.07592</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>761</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,37 +5709,37 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>560138</t>
+          <t>357537</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PASITOS SEGUROS</t>
+          <t>INNOVA SCHOOLS - LOS OLIVOS VILLA SOL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.99136</t>
+          <t>-11.96243</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.0757</t>
+          <t>-77.07092</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>828</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>578497</t>
+          <t>696491</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE LOS OLIVOS</t>
+          <t>CATOLICO SAN PIO X</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.940858</t>
+          <t>-11.99521</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.078303</t>
+          <t>-77.06437</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>384</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>644483</t>
+          <t>311158</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS HELICOIDAL PALMERAS</t>
+          <t>PNP PRECURSORES DE LA INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.987933</t>
+          <t>-11.95781</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.077967</t>
+          <t>-77.06849</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>740</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>646161</t>
+          <t>311040</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SAN PIO X - LOS OLIVOS / SAN PIO X- LOS OLIVOS</t>
+          <t>2096 PERU JAPON</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.99595</t>
+          <t>-11.9802</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.06654</t>
+          <t>-77.0683</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>649758</t>
+          <t>311200</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>JUAN XXIII DE LOS OLIVOS</t>
+          <t>PALMAS REALES</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.94979</t>
+          <t>-11.9933</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.07984</t>
+          <t>-77.079</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>638</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6019,32 +6019,32 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>694374</t>
+          <t>311083</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FRIEDERICH GAUSS</t>
+          <t>3080 PERU - CANADA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-12.00735</t>
+          <t>-11.9558</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-77.07723</t>
+          <t>-77.07467</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>966</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>694393</t>
+          <t>311238</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE MAYOLO</t>
+          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.99615</t>
+          <t>-11.97452</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.08086</t>
+          <t>-77.06945</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>694500</t>
+          <t>313459</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CRISTO REY DE REYES</t>
+          <t>SKHOLE PAIDEA DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.9672</t>
+          <t>-11.99457</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.082033</t>
+          <t>-77.07712</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,37 +6205,37 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>695062</t>
+          <t>311224</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.99562</t>
+          <t>-11.9827</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.07578</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>982</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6267,37 +6267,37 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>695694</t>
+          <t>311931</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NIÑOS DE MARIA</t>
+          <t>ROBERT LETOURNEAU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.9712</t>
+          <t>-11.99529</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.0732</t>
+          <t>-77.06381</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>618</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6329,37 +6329,37 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>695788</t>
+          <t>310903</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FRANCISCO PENZOTTI</t>
+          <t>2015 MANUEL GONZALEZ PRADA</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.9669</t>
+          <t>-11.9954</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.0795</t>
+          <t>-77.06721</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>952</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6391,42 +6391,42 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>696009</t>
+          <t>311120</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>ARQUITECTOS SCHOOL DE LOS OLIVOS</t>
+          <t>3095 PERU KAWACHI</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.991662</t>
+          <t>-11.92235</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.070904</t>
+          <t>-77.07502</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>992</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6453,32 +6453,32 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>696245</t>
+          <t>310984</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>HONORES DE LOS OLIVOS</t>
+          <t>2087 REPUBLICA ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.98949</t>
+          <t>-11.9684</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.06573</t>
+          <t>-77.06865</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>696330</t>
+          <t>744072</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE QUIVES</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.98257</t>
+          <t>-11.96696</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.07094</t>
+          <t>-77.07281</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>696491</t>
+          <t>310998</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CATOLICO SAN PIO X</t>
+          <t>2089 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.99521</t>
+          <t>-11.987547</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.06437</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,42 +6639,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>696655</t>
+          <t>311002</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>2090 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-11.9672</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.082</t>
+          <t>-77.0735</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6701,37 +6701,37 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>696882</t>
+          <t>311484</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>LUMEN DEI</t>
+          <t>DIVINO MAESTRO DE PRO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.99255</t>
+          <t>-11.93312</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.06475</t>
+          <t>-77.07877</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>485</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6763,32 +6763,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>697075</t>
+          <t>312520</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CRUZ SACO</t>
+          <t>CARITAS DE AMOR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.98971</t>
+          <t>-11.98579</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.06518</t>
+          <t>-77.07284</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>97</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -6825,37 +6825,37 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>697122</t>
+          <t>312940</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA SCHOOL</t>
+          <t>MELITON CARVAJAL</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.95634</t>
+          <t>-11.97868</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.06569</t>
+          <t>-77.07671</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6887,32 +6887,32 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>697481</t>
+          <t>696009</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ILLARI</t>
+          <t>ARQUITECTOS SCHOOL DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.99251</t>
+          <t>-11.991662</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.07073</t>
+          <t>-77.070904</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -6949,42 +6949,42 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>698131</t>
+          <t>834789</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>MUNDO FELIZ KINDERGARTEN &amp; PRIMARY SCHOOL</t>
+          <t>INNOVA SCHOOLS - LOS OLIVOS SANTA ANA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.93763</t>
+          <t>-11.951</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.07844</t>
+          <t>-77.07792</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7011,42 +7011,42 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>698697</t>
+          <t>311115</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GOTITAS DE AMOR</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-12.00611</t>
+          <t>-11.94144</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.08073</t>
+          <t>-77.076683</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>727690</t>
+          <t>311101</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TRILCE LOS OLIVOS DE PROLIMA</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-11.92709</t>
+          <t>-11.9823</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.07332</t>
+          <t>-77.07145</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>744072</t>
+          <t>333099</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>2028 PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.96696</t>
+          <t>-11.9693</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.07281</t>
+          <t>-77.0774</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>745547</t>
+          <t>310960</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS LOS OLIVOS</t>
+          <t>2071 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.935869</t>
+          <t>-11.99395</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.079397</t>
+          <t>-77.07665</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>751604</t>
+          <t>646161</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CONSUELO VALLEJOS</t>
+          <t>SAN PIO X - LOS OLIVOS / SAN PIO X- LOS OLIVOS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.95436</t>
+          <t>-11.99595</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.07228</t>
+          <t>-77.06654</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>947</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>755536</t>
+          <t>778095</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PEREGRINOS DEL SEÑOR</t>
+          <t>VISIONARIOS COLEGIO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.97344</t>
+          <t>-11.96155</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.07318</t>
+          <t>-77.07104</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>458</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>778095</t>
+          <t>310941</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>VISIONARIOS COLEGIO</t>
+          <t>2025 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.96155</t>
+          <t>-11.945275</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.07104</t>
+          <t>-77.0746</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>780017</t>
+          <t>311016</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>SAN VICENTE FERRER</t>
+          <t>2091 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.92672</t>
+          <t>-11.98945</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.07374</t>
+          <t>-77.07302</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7507,42 +7507,42 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>780569</t>
+          <t>311219</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JULIO REY PASTOR</t>
+          <t>ALFREDO REBAZA ACOSTA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-11.9495</t>
+          <t>-12.0032</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.0847</t>
+          <t>-77.0665</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>783520</t>
+          <t>310936</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA - SEDE SANTA LUISA</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.95345</t>
+          <t>-11.95047</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.0719</t>
+          <t>-77.08175</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>812792</t>
+          <t>727690</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOS OLIVOS</t>
+          <t>TRILCE LOS OLIVOS DE PROLIMA</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-11.94956</t>
+          <t>-11.92709</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.07376</t>
+          <t>-77.07332</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>832422</t>
+          <t>310979</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>2078 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-11.99284</t>
+          <t>-11.9553</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.06999</t>
+          <t>-77.0712</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>78</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>834789</t>
+          <t>310719</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - LOS OLIVOS SANTA ANA</t>
+          <t>0013 PASTORCITOS DE FATIMA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-11.951</t>
+          <t>-11.9641</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.07792</t>
+          <t>-77.0804</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>213</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7817,32 +7817,32 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>837882</t>
+          <t>310724</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN MARTIN</t>
+          <t>014 MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>-11.990949</t>
+          <t>-11.97421</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>-77.08069</t>
+          <t>-77.07526</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>204</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>857785</t>
+          <t>695788</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>FRANCISCO PENZOTTI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-11.93341</t>
+          <t>-11.9669</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.07339</t>
+          <t>-77.0795</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>91</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,37 +7941,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>865785</t>
+          <t>780569</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LA RECOLETA DE LOS OLIVOS</t>
+          <t>JULIO REY PASTOR</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-11.957012</t>
+          <t>-11.9495</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.074954</t>
+          <t>-77.0847</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>313096</t>
+          <t>311035</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MANUEL DUATO</t>
+          <t>2095 HERMAN BUSSE DE LA GUERRA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-11.99665</t>
+          <t>-11.9354</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.06843</t>
+          <t>-77.0746</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">

--- a/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>312172</t>
+          <t>865785</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JAHDAI</t>
+          <t>LA RECOLETA DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-11.991662</t>
+          <t>396</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-77.070904</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.957012</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.074954</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>528285</t>
+          <t>857785</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ANDREAS VESALIUS</t>
+          <t>JOSE MARIA ARGUEDAS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-11.991662</t>
+          <t>217</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-77.070904</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.93341</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.07339</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>560138</t>
+          <t>837882</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>PASITOS SEGUROS</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN MARTIN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-11.99136</t>
+          <t>336</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-77.0757</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.990949</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.08069</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,42 +687,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>695694</t>
+          <t>834789</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NIÑOS DE MARIA</t>
+          <t>INNOVA SCHOOLS - LOS OLIVOS SANTA ANA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-11.9712</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-77.0732</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.951</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.07792</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>313096</t>
+          <t>832422</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MANUEL DUATO</t>
+          <t>PITAGORAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-11.99665</t>
+          <t>546</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-77.06843</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-11.99284</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-77.06999</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>312493</t>
+          <t>812792</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>HANS CHRISTIAN</t>
+          <t>SAN IGNACIO DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-11.94487</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-77.07658</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>-11.94956</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.07376</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>698131</t>
+          <t>783520</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MUNDO FELIZ KINDERGARTEN &amp; PRIMARY SCHOOL</t>
+          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA - SEDE SANTA LUISA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-11.93763</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-77.07844</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>-11.95345</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-77.0719</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>310696</t>
+          <t>780569</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0001 NIÑO JESUS DE PRAGA</t>
+          <t>JULIO REY PASTOR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-11.92268</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-77.075</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-11.9495</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.0847</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>310762</t>
+          <t>780017</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0318 CARMELITAS</t>
+          <t>SAN VICENTE FERRER</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-11.98231</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-11.92672</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.07374</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>310804</t>
+          <t>778095</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0346 LAS PALMERAS</t>
+          <t>VISIONARIOS COLEGIO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-11.98773</t>
+          <t>458</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-77.07176</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-11.96155</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.07104</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>310818</t>
+          <t>755536</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0348 SANTA LUISA</t>
+          <t>PEREGRINOS DEL SEÑOR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-11.95574</t>
+          <t>209</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-77.07155</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-11.97344</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.07318</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>310837</t>
+          <t>751604</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>CONSUELO VALLEJOS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-11.97014</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-77.068534</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>-11.95436</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.07228</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>311295</t>
+          <t>745547</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0025 CONFRATERNIDAD PERUANO - MEXICANO</t>
+          <t>TECHNOLOGY SCHOOLS LOS OLIVOS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-11.9534</t>
+          <t>315</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-77.0834</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>-11.935869</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.079397</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>857785</t>
+          <t>744072</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>JOSE MARIA ARGUEDAS</t>
+          <t>SACO OLIVEROS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-11.93341</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-77.07339</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>-11.96696</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-77.07281</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>313478</t>
+          <t>727690</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAN VICENTE FERRER</t>
+          <t>TRILCE LOS OLIVOS DE PROLIMA</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-11.99345</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-77.0756</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>-11.92709</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>-77.07332</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1431,37 +1431,37 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>310700</t>
+          <t>698697</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0008 PEQUEÑO BENJAMIN</t>
+          <t>GOTITAS DE AMOR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-11.93757</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-77.07621</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>-12.00611</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.08073</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1493,37 +1493,37 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>310842</t>
+          <t>698131</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0377 DIVINO NIÑO JESUS</t>
+          <t>MUNDO FELIZ KINDERGARTEN &amp; PRIMARY SCHOOL</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-11.98246</t>
+          <t>127</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-77.07006</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>-11.93763</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.07844</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>311257</t>
+          <t>697481</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0022 SEMILLITAS DEL FUTURO</t>
+          <t>ILLARI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-11.98813</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-77.0792</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>-11.99251</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.07073</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>312596</t>
+          <t>697122</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LATINOAMERICANO</t>
+          <t>SAN LUIS GONZAGA SCHOOL</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-11.9679</t>
+          <t>352</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-77.0827</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-11.95634</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.06569</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,37 +1679,37 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>312676</t>
+          <t>697075</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
+          <t>CRUZ SACO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-11.965</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-77.06943</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-11.98971</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-77.06518</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1741,37 +1741,37 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>310776</t>
+          <t>696882</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0327 ALMIRANTE GRAU</t>
+          <t>LUMEN DEI</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-11.9856</t>
+          <t>43</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-77.071</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>-11.99255</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.06475</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>310823</t>
+          <t>696655</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0351 SAN MARTIN DE PORRES</t>
+          <t>SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-11.9965</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-77.0782</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-11.9672</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.082</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>311196</t>
+          <t>696491</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>CATOLICO SAN PIO X</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-11.94905</t>
+          <t>384</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-77.0725</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>-11.99521</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.06437</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>311304</t>
+          <t>696330</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0026 SAN ROQUE</t>
+          <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-11.9582</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-77.0766</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>-11.98257</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.07094</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>313058</t>
+          <t>696245</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>RAYITO DE LUNA</t>
+          <t>HONORES DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-11.93719</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-77.07714</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-11.98949</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.06573</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,37 +2051,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>313384</t>
+          <t>696009</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS DE LOS OLIVOS</t>
+          <t>ARQUITECTOS SCHOOL DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-12.00696</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-77.07008</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-11.991662</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.070904</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>545497</t>
+          <t>695788</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INYARI</t>
+          <t>FRANCISCO PENZOTTI</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-12.00761</t>
+          <t>91</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-77.07085</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>-11.9669</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0795</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>695062</t>
+          <t>695694</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>ISAAC NEWTON</t>
+          <t>NIÑOS DE MARIA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-11.99562</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-77.07578</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>-11.9712</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.0732</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,37 +2237,37 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>755536</t>
+          <t>695062</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PEREGRINOS DEL SEÑOR</t>
+          <t>ISAAC NEWTON</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-11.97344</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-77.07318</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>-11.99562</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.07578</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>812792</t>
+          <t>694500</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOS OLIVOS</t>
+          <t>CRISTO REY DE REYES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-11.94956</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-77.07376</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>-11.9672</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-77.082033</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>311281</t>
+          <t>694393</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>LOS LIBERTADORES</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE MAYOLO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-11.9807</t>
+          <t>238</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-77.0739</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>-11.99615</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.08086</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>313124</t>
+          <t>694374</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>FRIEDERICH GAUSS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-12.006026</t>
+          <t>287</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-77.068613</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>-12.00735</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.07723</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>313143</t>
+          <t>649758</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>STANFORD SUIZA PERUANA</t>
+          <t>JUAN XXIII DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-11.97634</t>
+          <t>270</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-77.07393</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>-11.94979</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.07984</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>694374</t>
+          <t>646161</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FRIEDERICH GAUSS</t>
+          <t>SAN PIO X - LOS OLIVOS / SAN PIO X- LOS OLIVOS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-12.00735</t>
+          <t>947</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-77.07723</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>-11.99595</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-77.06654</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>310757</t>
+          <t>644483</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>018 OKINAWA</t>
+          <t>SACO OLIVEROS HELICOIDAL PALMERAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-11.9502</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-77.08179</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>-11.987933</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.077967</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>310917</t>
+          <t>578497</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2016 CHAVIN DE HUANTAR</t>
+          <t>NUESTRA SEÑORA DE MONSERRAT DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-11.98506</t>
+          <t>478</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-77.07347</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>-11.940858</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.078303</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>312271</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WILLIAM PRESCOTT</t>
+          <t>PASITOS SEGUROS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-11.99218</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-77.07909</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-11.99136</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.0757</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>694393</t>
+          <t>545497</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE MAYOLO</t>
+          <t>INYARI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-11.99615</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-77.08086</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-12.00761</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.07085</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,37 +2857,37 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>865785</t>
+          <t>528285</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>LA RECOLETA DE LOS OLIVOS</t>
+          <t>ANDREAS VESALIUS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-11.957012</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-77.074954</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>-11.991662</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-77.070904</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>312997</t>
+          <t>357537</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>INNOVA SCHOOLS - LOS OLIVOS VILLA SOL</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-11.9956</t>
+          <t>828</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-77.0697</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>-11.96243</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>-77.07092</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>312935</t>
+          <t>333099</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE QUIVES</t>
+          <t>2028 PERUANO BRITANICO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-11.98249</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-77.07059</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>-11.9693</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.0774</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,37 +3043,37 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>697075</t>
+          <t>313529</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CRUZ SACO</t>
+          <t>SAN ANDRES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-11.98971</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-77.06518</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-11.92587</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-77.07339</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>310955</t>
+          <t>313478</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
+          <t>SAN VICENTE FERRER</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-11.9897</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-77.0778</t>
+          <t>111</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-11.99345</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.0756</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>311356</t>
+          <t>313459</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BADEN POWELL</t>
+          <t>SKHOLE PAIDEA DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-12.00838</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-77.07387</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>-11.99457</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.07712</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>694500</t>
+          <t>313384</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>CRISTO REY DE REYES</t>
+          <t>SAN JUAN DE DIOS DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-11.9672</t>
+          <t>265</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-77.082033</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>-12.00696</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.07008</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>696330</t>
+          <t>313303</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE QUIVES</t>
+          <t>SAN PABLO APOSTOL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-11.98257</t>
+          <t>735</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-77.07094</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>-11.93901</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.07557</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3353,32 +3353,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>780017</t>
+          <t>313143</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SAN VICENTE FERRER</t>
+          <t>STANFORD SUIZA PERUANA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-11.92672</t>
+          <t>221</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-77.07374</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-11.97634</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-77.07393</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>311342</t>
+          <t>313124</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BARBARA D'ACHILLE SCHOOL</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-11.96123</t>
+          <t>228</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-77.07379</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-12.006026</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-77.068613</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>649758</t>
+          <t>313096</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>JUAN XXIII DE LOS OLIVOS</t>
+          <t>MANUEL DUATO</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-11.94979</t>
+          <t>497</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-77.07984</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>-11.99665</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.06843</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3539,32 +3539,32 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>837882</t>
+          <t>313063</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE SAN MARTIN</t>
+          <t>GALILEO GALILEI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-11.990949</t>
+          <t>200</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-77.08069</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>-11.94887</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-77.07775</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>696882</t>
+          <t>313058</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>LUMEN DEI</t>
+          <t>RAYITO DE LUNA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-11.99255</t>
+          <t>282</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-77.06475</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-11.93719</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.07714</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>698697</t>
+          <t>312997</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GOTITAS DE AMOR</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-12.00611</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-77.08073</t>
+          <t>151</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-11.9956</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>-77.0697</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,37 +3725,37 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>751604</t>
+          <t>312940</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CONSUELO VALLEJOS</t>
+          <t>MELITON CARVAJAL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-11.95436</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-77.07228</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>-11.97868</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.07671</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>783520</t>
+          <t>312935</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA - SEDE SANTA LUISA</t>
+          <t>SANTA ROSA DE QUIVES</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-11.95345</t>
+          <t>405</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-77.0719</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-11.98249</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-77.07059</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -3859,22 +3859,22 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>-11.94461</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>-77.07437</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -3911,32 +3911,32 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>313529</t>
+          <t>312676</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SAN ANDRES</t>
+          <t>NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-11.92587</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-77.07339</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>-11.965</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-77.06943</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -3973,32 +3973,32 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>697122</t>
+          <t>312596</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SAN LUIS GONZAGA SCHOOL</t>
+          <t>LATINOAMERICANO</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-11.95634</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-77.06569</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>-11.9679</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.0827</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4035,42 +4035,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>745547</t>
+          <t>312520</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>TECHNOLOGY SCHOOLS LOS OLIVOS</t>
+          <t>CARITAS DE AMOR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-11.935869</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-77.079397</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>-11.98579</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-77.07284</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4097,37 +4097,37 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>312054</t>
+          <t>312493</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>HANS CHRISTIAN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-11.98264</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-77.07993</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>-11.94487</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.07658</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4159,32 +4159,32 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>696245</t>
+          <t>312290</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>HONORES DE LOS OLIVOS</t>
+          <t>BH SCHOOL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-11.98949</t>
+          <t>664</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-77.06573</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-11.97959</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-77.07473</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4221,32 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>310861</t>
+          <t>312271</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2004 SEÑOR DE LOS MILAGROS</t>
+          <t>WILLIAM PRESCOTT</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-11.97676</t>
+          <t>214</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-77.07872</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>-11.99218</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.07909</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4283,42 +4283,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>310875</t>
+          <t>312172</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2005 LOS OLIVOS</t>
+          <t>JAHDAI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-12.01125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-77.0792</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>-11.991662</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.070904</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4345,32 +4345,32 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>311059</t>
+          <t>312167</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>SANTA MARIA DE LA PROVIDENCIA</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-12.00308</t>
+          <t>684</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-77.06257</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>-11.99241</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.07804</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4407,37 +4407,37 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>311078</t>
+          <t>312110</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>3078 HEROES DEL CENEPA</t>
+          <t>SANTA CECILIA DE LOS OLIVOS</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-12.0037</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-77.0817</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-11.97163</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.07287</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -4469,37 +4469,37 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>311610</t>
+          <t>312054</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PAMER CARLOS IZAGUIRRE</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-11.99119</t>
+          <t>342</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-77.08025</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>-11.98264</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.07993</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4531,32 +4531,32 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>313063</t>
+          <t>312025</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GALILEO GALILEI</t>
+          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-11.94887</t>
+          <t>389</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-77.07775</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>-11.98614</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-77.0704</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4593,32 +4593,32 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>311021</t>
+          <t>311931</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2092 CRISTO MORADO</t>
+          <t>ROBERT LETOURNEAU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>-11.99961</t>
+          <t>618</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>-77.0754</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>-11.99529</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-77.06381</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4665,22 +4665,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>-11.97935</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>-77.08188</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4717,32 +4717,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>312025</t>
+          <t>311610</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA DE LA SALLE</t>
+          <t>PAMER CARLOS IZAGUIRRE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>-11.98614</t>
+          <t>615</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-77.0704</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>-11.99119</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-77.08025</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4779,32 +4779,32 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>312167</t>
+          <t>311484</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE LA PROVIDENCIA</t>
+          <t>DIVINO MAESTRO DE PRO</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>-11.99241</t>
+          <t>485</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-77.07804</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>-11.93312</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-77.07877</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -4841,42 +4841,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>312110</t>
+          <t>311436</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SANTA CECILIA DE LOS OLIVOS</t>
+          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>-11.97163</t>
+          <t>448</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-77.07287</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-11.9734</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.0843</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -4903,32 +4903,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>697481</t>
+          <t>311356</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ILLARI</t>
+          <t>BADEN POWELL</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-11.99251</t>
+          <t>151</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-77.07073</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-12.00838</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-77.07387</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>313303</t>
+          <t>311342</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SAN PABLO APOSTOL</t>
+          <t>BARBARA D'ACHILLE SCHOOL</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-11.93901</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-77.07557</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>-11.96123</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.07379</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>832422</t>
+          <t>311304</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PITAGORAS</t>
+          <t>0026 SAN ROQUE</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-11.99284</t>
+          <t>306</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-77.06999</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>-11.9582</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-77.0766</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5089,32 +5089,32 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>696655</t>
+          <t>311295</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SAN JUAN BAUTISTA</t>
+          <t>0025 CONFRATERNIDAD PERUANO - MEXICANO</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-11.9672</t>
+          <t>243</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-77.082</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>-11.9534</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-77.0834</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>310880</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-12.00754</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-77.07722</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>-11.9807</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.0739</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5213,32 +5213,32 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>578497</t>
+          <t>311257</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE MONSERRAT DE LOS OLIVOS</t>
+          <t>0022 SEMILLITAS DEL FUTURO</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-11.940858</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-77.078303</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>-11.98813</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>-77.0792</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -5275,32 +5275,32 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>311144</t>
+          <t>311238</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>JOSE ABELARDO QUIÑONEZ GONZALES</t>
+          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-12.007857</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>-77.063833</t>
+          <t>47</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>-11.97452</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-77.06945</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5337,32 +5337,32 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>311182</t>
+          <t>311224</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NUEVO PERU</t>
+          <t>JORGE BASADRE GROHMANN</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-11.96896</t>
+          <t>982</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-77.0782</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>-11.9827</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -5399,32 +5399,32 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>312290</t>
+          <t>311219</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BH SCHOOL</t>
+          <t>ALFREDO REBAZA ACOSTA</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-11.97959</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>-77.07473</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>-12.0032</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-77.0665</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -5461,32 +5461,32 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>311436</t>
+          <t>311200</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CORAZON DE JESUS PIONERO DE LA CIENCIA</t>
+          <t>PALMAS REALES</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-11.9734</t>
+          <t>638</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>-77.0843</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>448</t>
+          <t>-11.9933</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.079</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -5523,32 +5523,32 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>644483</t>
+          <t>311196</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS HELICOIDAL PALMERAS</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-11.987933</t>
+          <t>317</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-77.077967</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-11.94905</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-77.0725</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5585,32 +5585,32 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>310899</t>
+          <t>311182</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2007 ROSA DE LAS AMERICAS</t>
+          <t>NUEVO PERU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-11.98205</t>
+          <t>949</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-77.08295</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>-11.96896</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-77.0782</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -5657,22 +5657,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
+          <t>761</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
           <t>-12.0049</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>-77.07592</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -5709,32 +5709,32 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>357537</t>
+          <t>311158</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - LOS OLIVOS VILLA SOL</t>
+          <t>PNP PRECURSORES DE LA INDEPENDENCIA NACIONAL</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-11.96243</t>
+          <t>740</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-77.07092</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>828</t>
+          <t>-11.95781</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.06849</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>696491</t>
+          <t>311144</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>CATOLICO SAN PIO X</t>
+          <t>JOSE ABELARDO QUIÑONEZ GONZALES</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-11.99521</t>
+          <t>872</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-77.06437</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>-12.007857</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-77.063833</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>311158</t>
+          <t>311120</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PNP PRECURSORES DE LA INDEPENDENCIA NACIONAL</t>
+          <t>3095 PERU KAWACHI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-11.95781</t>
+          <t>992</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-77.06849</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>-11.92235</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-77.07502</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -5895,32 +5895,32 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>311040</t>
+          <t>311115</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2096 PERU JAPON</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>-11.9802</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>-77.0683</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>-11.94144</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-77.076683</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5957,32 +5957,32 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>311200</t>
+          <t>311101</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>PALMAS REALES</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-11.9933</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-77.079</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>-11.9823</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-77.07145</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6029,22 +6029,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
           <t>-11.9558</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>-77.07467</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>311238</t>
+          <t>311078</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GRAN MARISCAL TORIBIO DE LUZURIAGA</t>
+          <t>3078 HEROES DEL CENEPA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-11.97452</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-77.06945</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>-12.0037</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>-77.0817</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6143,37 +6143,37 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>313459</t>
+          <t>311059</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SKHOLE PAIDEA DE LOS OLIVOS</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-11.99457</t>
+          <t>517</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>-77.07712</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-12.00308</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>-77.06257</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>311224</t>
+          <t>311040</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>JORGE BASADRE GROHMANN</t>
+          <t>2096 PERU JAPON</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>-11.9827</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>-11.9802</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.0683</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6267,32 +6267,32 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>311931</t>
+          <t>311035</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>ROBERT LETOURNEAU</t>
+          <t>2095 HERMAN BUSSE DE LA GUERRA</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>-11.99529</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>-77.06381</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>-11.9354</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-77.0746</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6329,32 +6329,32 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>310903</t>
+          <t>311021</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2015 MANUEL GONZALEZ PRADA</t>
+          <t>2092 CRISTO MORADO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>-11.9954</t>
+          <t>482</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>-77.06721</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>-11.99961</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.0754</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -6391,32 +6391,32 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>311120</t>
+          <t>311016</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>3095 PERU KAWACHI</t>
+          <t>2091 MARISCAL ANDRES AVELINO CACERES</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>-11.92235</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>-77.07502</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>-11.98945</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>-77.07302</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -6453,42 +6453,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>310984</t>
+          <t>311002</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2087 REPUBLICA ORIENTAL DEL URUGUAY</t>
+          <t>2090 VIRGEN DE LA PUERTA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>-11.9684</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>-77.06865</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>-12.01</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-77.0735</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6515,32 +6515,32 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>744072</t>
+          <t>310998</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SACO OLIVEROS</t>
+          <t>2089 MICAELA BASTIDAS</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>-11.96696</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>-77.07281</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>-11.987547</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6577,32 +6577,32 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>310998</t>
+          <t>310984</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2089 MICAELA BASTIDAS</t>
+          <t>2087 REPUBLICA ORIENTAL DEL URUGUAY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>-11.987547</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>-77.0667</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>-11.9684</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>-77.06865</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6639,42 +6639,42 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>311002</t>
+          <t>310979</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2090 VIRGEN DE LA PUERTA</t>
+          <t>2078 NUESTRA SEÑORA DE LOURDES</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-12.01</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>-77.0735</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>-11.9553</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-77.0712</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6701,32 +6701,32 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>311484</t>
+          <t>310960</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>DIVINO MAESTRO DE PRO</t>
+          <t>2071 CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-11.93312</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>-77.07877</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>-11.99395</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-77.07665</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6763,42 +6763,42 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>312520</t>
+          <t>310955</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CARITAS DE AMOR</t>
+          <t>2035 CARLOS CHIYOTERU HIRAOKA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-11.98579</t>
+          <t>400</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>-77.07284</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>-11.9897</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.0778</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6825,42 +6825,42 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>312940</t>
+          <t>310941</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>MELITON CARVAJAL</t>
+          <t>2025 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-11.97868</t>
+          <t>1438</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>-77.07671</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-11.945275</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.0746</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -6887,37 +6887,37 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>696009</t>
+          <t>310936</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>ARQUITECTOS SCHOOL DE LOS OLIVOS</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>-11.991662</t>
+          <t>1732</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>-77.070904</t>
+          <t>74</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>-11.95047</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-77.08175</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>834789</t>
+          <t>310917</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS - LOS OLIVOS SANTA ANA</t>
+          <t>2016 CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-11.951</t>
+          <t>378</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-77.07792</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>-11.98506</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-77.07347</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7011,32 +7011,32 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>311115</t>
+          <t>310903</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>2015 MANUEL GONZALEZ PRADA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-11.94144</t>
+          <t>952</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>-77.076683</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>-11.9954</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-77.06721</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7073,32 +7073,32 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>311101</t>
+          <t>310899</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>2007 ROSA DE LAS AMERICAS</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>-11.9823</t>
+          <t>959</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>-77.07145</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>-11.98205</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.08295</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>333099</t>
+          <t>310880</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2028 PERUANO BRITANICO</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>-11.9693</t>
+          <t>753</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>-77.0774</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>-12.00754</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-77.07722</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7197,32 +7197,32 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>310960</t>
+          <t>310875</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2071 CESAR VALLEJO</t>
+          <t>2005 LOS OLIVOS</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>-11.99395</t>
+          <t>538</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>-77.07665</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>-12.01125</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.0792</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -7259,32 +7259,32 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>646161</t>
+          <t>310861</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SAN PIO X - LOS OLIVOS / SAN PIO X- LOS OLIVOS</t>
+          <t>2004 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>-11.99595</t>
+          <t>537</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>-77.06654</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>-11.97676</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-77.07872</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -7321,32 +7321,32 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>778095</t>
+          <t>310842</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>VISIONARIOS COLEGIO</t>
+          <t>0377 DIVINO NIÑO JESUS</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>-11.96155</t>
+          <t>240</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>-77.07104</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>-11.98246</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-77.07006</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -7383,32 +7383,32 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>310941</t>
+          <t>310837</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2025 INMACULADA CONCEPCION</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>-11.945275</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>-77.0746</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>-11.97014</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-77.068534</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>311016</t>
+          <t>310823</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2091 MARISCAL ANDRES AVELINO CACERES</t>
+          <t>0351 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>-11.98945</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>-77.07302</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1482</t>
+          <t>-11.9965</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-77.0782</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>311219</t>
+          <t>310818</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ALFREDO REBAZA ACOSTA</t>
+          <t>0348 SANTA LUISA</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>-12.0032</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>-77.0665</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>-11.95574</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-77.07155</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7569,32 +7569,32 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>310936</t>
+          <t>310804</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>0346 LAS PALMERAS</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>-11.95047</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>-77.08175</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>-11.98773</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>-77.07176</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -7631,32 +7631,32 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>727690</t>
+          <t>310776</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>TRILCE LOS OLIVOS DE PROLIMA</t>
+          <t>0327 ALMIRANTE GRAU</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>-11.92709</t>
+          <t>262</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>-77.07332</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>-11.9856</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-77.071</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -7693,32 +7693,32 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>310979</t>
+          <t>310762</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2078 NUESTRA SEÑORA DE LOURDES</t>
+          <t>0318 CARMELITAS</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>-11.9553</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>-77.0712</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>-11.98231</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>-77.0667</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -7755,32 +7755,32 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>310719</t>
+          <t>310757</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>0013 PASTORCITOS DE FATIMA</t>
+          <t>018 OKINAWA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>-11.9641</t>
+          <t>362</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>-77.0804</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>-11.9502</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.08179</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -7827,22 +7827,22 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
           <t>-11.97421</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>-77.07526</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -7879,37 +7879,37 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>695788</t>
+          <t>310719</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FRANCISCO PENZOTTI</t>
+          <t>0013 PASTORCITOS DE FATIMA</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>-11.9669</t>
+          <t>213</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>-77.0795</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>-11.9641</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.0804</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7941,37 +7941,37 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>780569</t>
+          <t>310700</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>JULIO REY PASTOR</t>
+          <t>0008 PEQUEÑO BENJAMIN</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>-11.9495</t>
+          <t>210</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>-77.0847</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-11.93757</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-77.07621</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8003,32 +8003,32 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>311035</t>
+          <t>310696</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2095 HERMAN BUSSE DE LA GUERRA</t>
+          <t>0001 NIÑO JESUS DE PRAGA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>-11.9354</t>
+          <t>237</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>-77.0746</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>-11.92268</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>-77.075</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
+++ b/ZonasEscolares/excels/LIMA-LIMA-LOS_OLIVOS.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
